--- a/public/StudentTemp.xlsx
+++ b/public/StudentTemp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">PEN / SR No</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t xml:space="preserve">Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section</t>
   </si>
   <si>
     <t xml:space="preserve">Session</t>
@@ -58,6 +55,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -79,6 +77,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -149,8 +148,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -174,9 +173,6 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/public/StudentTemp.xlsx
+++ b/public/StudentTemp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">PEN / SR No</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address</t>
   </si>
 </sst>
 </file>
@@ -148,8 +154,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -173,6 +179,12 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/public/StudentTemp.xlsx
+++ b/public/StudentTemp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">PEN / SR No</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport</t>
   </si>
 </sst>
 </file>
@@ -154,8 +157,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -184,6 +187,9 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/public/StudentTemp.xlsx
+++ b/public/StudentTemp.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">PEN / SR No</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">Father Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mother Name</t>
   </si>
   <si>
     <t xml:space="preserve">Mobile</t>
@@ -131,13 +134,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -152,13 +159,123 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.8"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -188,14 +305,17 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
